--- a/artfynd/A 21058-2026 artfynd.xlsx
+++ b/artfynd/A 21058-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133877393</v>
       </c>
       <c r="B2" t="n">
-        <v>97999</v>
+        <v>98003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,64 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133872434</v>
+        <v>133877396</v>
       </c>
       <c r="B3" t="n">
-        <v>99023</v>
+        <v>79953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>233</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Granholmen, Granholmen, Pi lm</t>
+          <t>Granholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701504</v>
+        <v>701424</v>
       </c>
       <c r="R3" t="n">
-        <v>7314616</v>
+        <v>7314621</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +871,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -906,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133877396</v>
+        <v>133877389</v>
       </c>
       <c r="B4" t="n">
         <v>79953</v>
@@ -941,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701424</v>
+        <v>701418</v>
       </c>
       <c r="R4" t="n">
-        <v>7314621</v>
+        <v>7314598</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133877389</v>
+        <v>133877395</v>
       </c>
       <c r="B5" t="n">
-        <v>79953</v>
+        <v>98003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701418</v>
+        <v>701424</v>
       </c>
       <c r="R5" t="n">
-        <v>7314598</v>
+        <v>7314622</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1093,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133877395</v>
+        <v>133877390</v>
       </c>
       <c r="B6" t="n">
-        <v>97999</v>
+        <v>79953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1155,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701424</v>
+        <v>701417</v>
       </c>
       <c r="R6" t="n">
-        <v>7314622</v>
+        <v>7314597</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1200,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1337,7 +1320,7 @@
         <v>133877400</v>
       </c>
       <c r="B8" t="n">
-        <v>97999</v>
+        <v>98003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,48 +1424,64 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133877390</v>
+        <v>133880760</v>
       </c>
       <c r="B9" t="n">
-        <v>79953</v>
+        <v>99027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>233</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Oakes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Granholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701417</v>
+        <v>701502</v>
       </c>
       <c r="R9" t="n">
-        <v>7314597</v>
+        <v>7314615</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1511,7 +1510,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1521,7 +1520,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1530,6 +1529,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1548,64 +1548,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133880760</v>
+        <v>133877416</v>
       </c>
       <c r="B10" t="n">
-        <v>99023</v>
+        <v>98003</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>233</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Granholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701502</v>
+        <v>701398</v>
       </c>
       <c r="R10" t="n">
-        <v>7314615</v>
+        <v>7314607</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1634,7 +1618,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1628,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,7 +1637,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1672,48 +1655,64 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133877416</v>
+        <v>133872434</v>
       </c>
       <c r="B11" t="n">
-        <v>97999</v>
+        <v>99027</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>233</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Oakes</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Granholmen, Pi lm</t>
+          <t>Granholmen, Granholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701398</v>
+        <v>701504</v>
       </c>
       <c r="R11" t="n">
-        <v>7314607</v>
+        <v>7314616</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1742,7 +1741,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,7 +1751,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,6 +1760,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21058-2026 artfynd.xlsx
+++ b/artfynd/A 21058-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133877393</v>
       </c>
       <c r="B2" t="n">
-        <v>98003</v>
+        <v>98005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133877395</v>
       </c>
       <c r="B5" t="n">
-        <v>98003</v>
+        <v>98005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,48 +1103,64 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133877390</v>
+        <v>133880760</v>
       </c>
       <c r="B6" t="n">
-        <v>79953</v>
+        <v>99029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>233</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Oakes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Granholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701417</v>
+        <v>701502</v>
       </c>
       <c r="R6" t="n">
-        <v>7314597</v>
+        <v>7314615</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,6 +1208,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1317,32 +1334,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133877400</v>
+        <v>133877390</v>
       </c>
       <c r="B8" t="n">
-        <v>98003</v>
+        <v>79953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,13 +1369,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701480</v>
+        <v>701417</v>
       </c>
       <c r="R8" t="n">
-        <v>7314616</v>
+        <v>7314597</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,7 +1404,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1414,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,64 +1441,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133880760</v>
+        <v>133877400</v>
       </c>
       <c r="B9" t="n">
-        <v>99027</v>
+        <v>98005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>233</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Granholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701502</v>
+        <v>701480</v>
       </c>
       <c r="R9" t="n">
-        <v>7314615</v>
+        <v>7314616</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1510,7 +1511,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1520,7 +1521,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,7 +1530,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>133877416</v>
       </c>
       <c r="B10" t="n">
-        <v>98003</v>
+        <v>98005</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>133872434</v>
       </c>
       <c r="B11" t="n">
-        <v>99027</v>
+        <v>99029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 21058-2026 artfynd.xlsx
+++ b/artfynd/A 21058-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133877393</v>
       </c>
       <c r="B2" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133877396</v>
       </c>
       <c r="B3" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>133877389</v>
       </c>
       <c r="B4" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133877395</v>
       </c>
       <c r="B5" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>133880760</v>
       </c>
       <c r="B7" t="n">
-        <v>99070</v>
+        <v>99077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>133877400</v>
       </c>
       <c r="B8" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>133877390</v>
       </c>
       <c r="B9" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>133877416</v>
       </c>
       <c r="B10" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>133872434</v>
       </c>
       <c r="B11" t="n">
-        <v>99070</v>
+        <v>99077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 21058-2026 artfynd.xlsx
+++ b/artfynd/A 21058-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133877393</v>
+        <v>16860295</v>
       </c>
       <c r="B2" t="n">
-        <v>98053</v>
+        <v>101224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Röd trolldruva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Actaea erythrocarpa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fisch.) Kom.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Granholmen, Pi lm</t>
+          <t>Dammberget,  2150 m ONO om trevägskorsningen, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701394</v>
+        <v>701472</v>
       </c>
       <c r="R2" t="n">
-        <v>7314585</v>
+        <v>7314644</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -738,24 +741,19 @@
           <t>Arvidsjaur</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>PL-Arv-0012</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2010-07-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,64 +764,89 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Rikområde</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Allis Zethraeus, Ulf Zethraeus, Ann-mari Sundkvist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133877396</v>
+        <v>133872434</v>
       </c>
       <c r="B3" t="n">
-        <v>79985</v>
+        <v>99084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>233</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Oakes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Granholmen, Pi lm</t>
+          <t>Granholmen, Granholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701424</v>
+        <v>701504</v>
       </c>
       <c r="R3" t="n">
-        <v>7314621</v>
+        <v>7314616</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,6 +894,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,48 +913,62 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133877389</v>
+        <v>133872602</v>
       </c>
       <c r="B4" t="n">
-        <v>79985</v>
+        <v>99084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>233</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Oakes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Granholmen, Pi lm</t>
+          <t>Granholmen, Granholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701418</v>
+        <v>701531</v>
       </c>
       <c r="R4" t="n">
-        <v>7314598</v>
+        <v>7314614</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +1034,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133877395</v>
+        <v>133877397</v>
       </c>
       <c r="B5" t="n">
-        <v>98053</v>
+        <v>99084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>233</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701424</v>
+        <v>701484</v>
       </c>
       <c r="R5" t="n">
-        <v>7314622</v>
+        <v>7314636</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,32 +1141,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133877406</v>
+        <v>133877399</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>99084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>233</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701532</v>
+        <v>701497</v>
       </c>
       <c r="R6" t="n">
-        <v>7314599</v>
+        <v>7314631</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133880760</v>
+        <v>133877401</v>
       </c>
       <c r="B7" t="n">
-        <v>99077</v>
+        <v>99084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,36 +1276,20 @@
           <t>(L.) Oakes</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Granholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701502</v>
+        <v>701511</v>
       </c>
       <c r="R7" t="n">
-        <v>7314615</v>
+        <v>7314636</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1306,7 +1328,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 plantorna</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,7 +1342,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1334,32 +1360,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133877400</v>
+        <v>133877402</v>
       </c>
       <c r="B8" t="n">
-        <v>98053</v>
+        <v>99084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>233</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1369,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701480</v>
+        <v>701487</v>
       </c>
       <c r="R8" t="n">
-        <v>7314616</v>
+        <v>7314641</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1404,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1414,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,48 +1467,52 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133877390</v>
+        <v>133877404</v>
       </c>
       <c r="B9" t="n">
-        <v>79985</v>
+        <v>99084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>233</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Granholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701417</v>
+        <v>701503</v>
       </c>
       <c r="R9" t="n">
-        <v>7314597</v>
+        <v>7314620</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1511,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1521,7 +1551,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>5 plantor blomande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1530,6 +1565,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1548,32 +1584,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133877416</v>
+        <v>133877405</v>
       </c>
       <c r="B10" t="n">
-        <v>98053</v>
+        <v>99084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>233</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1583,13 +1619,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701398</v>
+        <v>701515</v>
       </c>
       <c r="R10" t="n">
-        <v>7314607</v>
+        <v>7314632</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1618,7 +1654,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1628,7 +1664,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133872434</v>
+        <v>133880760</v>
       </c>
       <c r="B11" t="n">
-        <v>99077</v>
+        <v>99084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,7 +1721,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1702,14 +1738,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Granholmen, Granholmen, Pi lm</t>
+          <t>Granholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701504</v>
+        <v>701502</v>
       </c>
       <c r="R11" t="n">
-        <v>7314616</v>
+        <v>7314615</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1741,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1751,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1776,6 +1812,862 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133877389</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Granholmen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>701418</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7314598</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133877390</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Granholmen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>701417</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7314597</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133877396</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Granholmen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>701424</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7314621</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133877406</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Granholmen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>701532</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7314599</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133877393</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Granholmen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>701394</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7314585</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133877395</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Granholmen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>701424</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7314622</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133877400</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Granholmen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>701480</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7314616</v>
+      </c>
+      <c r="S18" t="n">
+        <v>8</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133877416</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Granholmen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>701398</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7314607</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21058-2026 artfynd.xlsx
+++ b/artfynd/A 21058-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -786,6 +791,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16860295</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133872434</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1031,6 +1046,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133872602</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133877397</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1245,6 +1270,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133877399</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1357,6 +1387,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133877401</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1464,6 +1499,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133877402</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1581,6 +1621,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133877404</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1688,6 +1733,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133877405</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1812,6 +1862,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133880760</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1919,6 +1974,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133877389</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2026,6 +2086,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133877390</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2133,6 +2198,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133877396</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2240,6 +2310,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133877406</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2347,6 +2422,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133877393</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2454,6 +2534,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133877395</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2561,6 +2646,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133877400</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2668,8 +2758,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133877416</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>